--- a/Midterm project/Data.xlsx
+++ b/Midterm project/Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brian\Documents\2026-2027\Fall 2026\Spatial Programming\Midterm project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAD79E4A-6BFB-4FA0-855B-4A92F2C2FE99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{101C2FF3-FFAD-4E85-914E-811566905BCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E503F96-01F1-4E5A-814D-AEDB9B51F5A6}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{6E503F96-01F1-4E5A-814D-AEDB9B51F5A6}"/>
   </bookViews>
   <sheets>
     <sheet name="ReadMe" sheetId="2" r:id="rId1"/>
@@ -90,26 +90,20 @@
     <t>Asp Avenue, across the street from &amp; facing Memorial Union</t>
   </si>
   <si>
-    <t>Trout street, facing away from Sarkeys</t>
+    <t>Trout Avenue, facing away from Sarkeys</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
